--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/22.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/22.xlsx
@@ -426,13 +426,13 @@
         <v>-7.439542078905679</v>
       </c>
       <c r="E2">
-        <v>-6.099245221048538</v>
+        <v>-4.722697806092933</v>
       </c>
       <c r="F2">
-        <v>-4.339108716384724</v>
+        <v>-4.351161462095457</v>
       </c>
       <c r="G2">
-        <v>-5.101644521960333</v>
+        <v>-4.697728171259395</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.11287966253343</v>
       </c>
       <c r="E3">
-        <v>-5.637848061355021</v>
+        <v>-5.547197068669475</v>
       </c>
       <c r="F3">
-        <v>-4.834679515109529</v>
+        <v>-4.122402833607957</v>
       </c>
       <c r="G3">
-        <v>-5.311884026977289</v>
+        <v>-4.583494486881303</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.056129382585656</v>
       </c>
       <c r="E4">
-        <v>-6.494001357245178</v>
+        <v>-6.124441650427216</v>
       </c>
       <c r="F4">
-        <v>-4.997264841991793</v>
+        <v>-4.21753503124766</v>
       </c>
       <c r="G4">
-        <v>-5.782587323387484</v>
+        <v>-4.350322832913815</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.16161534560628</v>
       </c>
       <c r="E5">
-        <v>-6.892547826186239</v>
+        <v>-6.656455833796345</v>
       </c>
       <c r="F5">
-        <v>-4.40873796679444</v>
+        <v>-4.232532623075345</v>
       </c>
       <c r="G5">
-        <v>-5.644226383119184</v>
+        <v>-4.071273638863108</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.40800398276966</v>
       </c>
       <c r="E6">
-        <v>-7.005112104594901</v>
+        <v>-7.764419455357021</v>
       </c>
       <c r="F6">
-        <v>-4.324489688460118</v>
+        <v>-4.206747202561003</v>
       </c>
       <c r="G6">
-        <v>-6.061457747979071</v>
+        <v>-4.521785918029288</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.73952009026926</v>
       </c>
       <c r="E7">
-        <v>-9.003591082815937</v>
+        <v>-8.427990337122981</v>
       </c>
       <c r="F7">
-        <v>-4.298086305863287</v>
+        <v>-4.29744514949352</v>
       </c>
       <c r="G7">
-        <v>-5.319345996622806</v>
+        <v>-4.185841688340666</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.10804756718342</v>
       </c>
       <c r="E8">
-        <v>-9.919225884796845</v>
+        <v>-8.270526238928268</v>
       </c>
       <c r="F8">
-        <v>-4.359363956117978</v>
+        <v>-4.179647991345819</v>
       </c>
       <c r="G8">
-        <v>-6.286343106461763</v>
+        <v>-4.585308665836823</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.44287278127066</v>
       </c>
       <c r="E9">
-        <v>-9.002218955191612</v>
+        <v>-9.705626822803049</v>
       </c>
       <c r="F9">
-        <v>-4.471535671233267</v>
+        <v>-3.892888734049103</v>
       </c>
       <c r="G9">
-        <v>-4.466082678785511</v>
+        <v>-4.574258064826736</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.67589161935244</v>
       </c>
       <c r="E10">
-        <v>-10.21010335573154</v>
+        <v>-8.799823337892795</v>
       </c>
       <c r="F10">
-        <v>-4.566702660303888</v>
+        <v>-3.830615386176248</v>
       </c>
       <c r="G10">
-        <v>-5.563965517065093</v>
+        <v>-4.447043731389162</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.73350861165518</v>
       </c>
       <c r="E11">
-        <v>-11.71261933215851</v>
+        <v>-10.2375957214321</v>
       </c>
       <c r="F11">
-        <v>-4.219845347934068</v>
+        <v>-3.659038959503997</v>
       </c>
       <c r="G11">
-        <v>-4.639018956665959</v>
+        <v>-4.56025445719562</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.55224162733596</v>
       </c>
       <c r="E12">
-        <v>-11.00119153707949</v>
+        <v>-10.37850371865477</v>
       </c>
       <c r="F12">
-        <v>-3.960183645117729</v>
+        <v>-3.787826067984639</v>
       </c>
       <c r="G12">
-        <v>-4.811180566890218</v>
+        <v>-4.027971703209441</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.07595540866581</v>
       </c>
       <c r="E13">
-        <v>-12.14800040867796</v>
+        <v>-11.3583251112204</v>
       </c>
       <c r="F13">
-        <v>-4.405630760666538</v>
+        <v>-3.458924447437901</v>
       </c>
       <c r="G13">
-        <v>-5.360188196940794</v>
+        <v>-3.501214249728306</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.27428661931671</v>
       </c>
       <c r="E14">
-        <v>-12.07542708423103</v>
+        <v>-11.78211782275422</v>
       </c>
       <c r="F14">
-        <v>-2.963950073243113</v>
+        <v>-3.27936752920708</v>
       </c>
       <c r="G14">
-        <v>-4.609710697006792</v>
+        <v>-3.424806858681927</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.13609248656971</v>
       </c>
       <c r="E15">
-        <v>-12.47384222742587</v>
+        <v>-12.46181007198749</v>
       </c>
       <c r="F15">
-        <v>-3.35756458366395</v>
+        <v>-3.238408074608256</v>
       </c>
       <c r="G15">
-        <v>-5.15248456980692</v>
+        <v>-3.007373550544144</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.67704594716476</v>
       </c>
       <c r="E16">
-        <v>-14.01357320324788</v>
+        <v>-13.02703608372887</v>
       </c>
       <c r="F16">
-        <v>-3.483162477643814</v>
+        <v>-2.91721524111197</v>
       </c>
       <c r="G16">
-        <v>-3.61279949767498</v>
+        <v>-2.658908837625998</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.92839056029888</v>
       </c>
       <c r="E17">
-        <v>-14.25451971977399</v>
+        <v>-13.96410868166209</v>
       </c>
       <c r="F17">
-        <v>-2.629008825962563</v>
+        <v>-2.697610900792807</v>
       </c>
       <c r="G17">
-        <v>-2.33003262266372</v>
+        <v>-2.008048963514204</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.94106416411516</v>
       </c>
       <c r="E18">
-        <v>-13.47988801296992</v>
+        <v>-14.52741009195022</v>
       </c>
       <c r="F18">
-        <v>-2.220271640236217</v>
+        <v>-2.420119417998612</v>
       </c>
       <c r="G18">
-        <v>-2.92749339722707</v>
+        <v>-1.143529790843387</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.77938578585208</v>
       </c>
       <c r="E19">
-        <v>-17.11263439039708</v>
+        <v>-15.32065382692582</v>
       </c>
       <c r="F19">
-        <v>-2.589918168224454</v>
+        <v>-2.025676540174974</v>
       </c>
       <c r="G19">
-        <v>-1.968862035965851</v>
+        <v>-1.441833117750496</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.51685930147579</v>
       </c>
       <c r="E20">
-        <v>-16.6379733303351</v>
+        <v>-15.96598854386289</v>
       </c>
       <c r="F20">
-        <v>-2.574708514341653</v>
+        <v>-1.704096859101581</v>
       </c>
       <c r="G20">
-        <v>-2.354411480014913</v>
+        <v>-1.955411289439793</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.22778051823242</v>
       </c>
       <c r="E21">
-        <v>-17.65453423252496</v>
+        <v>-16.32385120231904</v>
       </c>
       <c r="F21">
-        <v>-1.924328273544663</v>
+        <v>-1.508914446551753</v>
       </c>
       <c r="G21">
-        <v>-2.553997649486494</v>
+        <v>-1.040346707475383</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.97900710953004</v>
       </c>
       <c r="E22">
-        <v>-17.82953711055138</v>
+        <v>-16.86028517631965</v>
       </c>
       <c r="F22">
-        <v>-1.85358404061078</v>
+        <v>-1.241015458281976</v>
       </c>
       <c r="G22">
-        <v>-1.597925339927133</v>
+        <v>-1.720577741611591</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.83599962383631</v>
       </c>
       <c r="E23">
-        <v>-18.43721303764066</v>
+        <v>-17.4629209118384</v>
       </c>
       <c r="F23">
-        <v>-1.5766889823466</v>
+        <v>-1.246799947855725</v>
       </c>
       <c r="G23">
-        <v>-1.992757553668311</v>
+        <v>-1.625531979179115</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.84873916132231</v>
       </c>
       <c r="E24">
-        <v>-18.55260308383011</v>
+        <v>-19.0987008213631</v>
       </c>
       <c r="F24">
-        <v>-1.783833020192853</v>
+        <v>-0.9355127317621155</v>
       </c>
       <c r="G24">
-        <v>-2.842170707043433</v>
+        <v>-0.5799822447843317</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.055003667485758</v>
       </c>
       <c r="E25">
-        <v>-18.66478244194812</v>
+        <v>-17.79022089921678</v>
       </c>
       <c r="F25">
-        <v>-1.5036021263976</v>
+        <v>-0.8472419013198002</v>
       </c>
       <c r="G25">
-        <v>-2.367911884724061</v>
+        <v>-1.602477340043631</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.470036214646237</v>
       </c>
       <c r="E26">
-        <v>-19.57783148527065</v>
+        <v>-18.6748084834011</v>
       </c>
       <c r="F26">
-        <v>-1.322133336201117</v>
+        <v>-0.6546307411882618</v>
       </c>
       <c r="G26">
-        <v>-2.074723350675126</v>
+        <v>-1.534448939757147</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.101652533559948</v>
       </c>
       <c r="E27">
-        <v>-19.18514486169552</v>
+        <v>-18.75247634110666</v>
       </c>
       <c r="F27">
-        <v>-1.203579050247258</v>
+        <v>-0.7796139865552485</v>
       </c>
       <c r="G27">
-        <v>-2.659776200557288</v>
+        <v>-1.499416746860579</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.940279943049889</v>
       </c>
       <c r="E28">
-        <v>-19.80502049776146</v>
+        <v>-18.77478813254245</v>
       </c>
       <c r="F28">
-        <v>-1.136212899581991</v>
+        <v>-0.6867059553920615</v>
       </c>
       <c r="G28">
-        <v>-3.125305114289602</v>
+        <v>-1.686813487656564</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.969096657724844</v>
       </c>
       <c r="E29">
-        <v>-19.2083985757249</v>
+        <v>-19.1220224625026</v>
       </c>
       <c r="F29">
-        <v>-1.153805766482647</v>
+        <v>-0.9147430758717234</v>
       </c>
       <c r="G29">
-        <v>-2.823913048394353</v>
+        <v>-1.887022039689528</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.157395356824068</v>
       </c>
       <c r="E30">
-        <v>-20.67431995369589</v>
+        <v>-18.16151501157968</v>
       </c>
       <c r="F30">
-        <v>-1.143951507858944</v>
+        <v>-1.047107074797654</v>
       </c>
       <c r="G30">
-        <v>-3.103971958834538</v>
+        <v>-1.966402300630173</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.466760068622968</v>
       </c>
       <c r="E31">
-        <v>-19.17044996354063</v>
+        <v>-18.72998793918457</v>
       </c>
       <c r="F31">
-        <v>-1.423297705268007</v>
+        <v>-1.127984726169983</v>
       </c>
       <c r="G31">
-        <v>-3.496937024891567</v>
+        <v>-1.743503269471044</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.855913063480344</v>
       </c>
       <c r="E32">
-        <v>-18.70642628892266</v>
+        <v>-18.47021655620857</v>
       </c>
       <c r="F32">
-        <v>-1.798850492838205</v>
+        <v>-0.9724496342529454</v>
       </c>
       <c r="G32">
-        <v>-3.026071511749948</v>
+        <v>-1.831169825896484</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.286571509461313</v>
       </c>
       <c r="E33">
-        <v>-18.42399895048628</v>
+        <v>-18.60627002929501</v>
       </c>
       <c r="F33">
-        <v>-1.636420899027667</v>
+        <v>-1.542204047368056</v>
       </c>
       <c r="G33">
-        <v>-2.677010900634733</v>
+        <v>-1.960943211035915</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.730262570930737</v>
       </c>
       <c r="E34">
-        <v>-18.50451521834266</v>
+        <v>-18.49280005608482</v>
       </c>
       <c r="F34">
-        <v>-1.869521829440642</v>
+        <v>-1.29889431708298</v>
       </c>
       <c r="G34">
-        <v>-2.086124869512376</v>
+        <v>-0.9339325316610499</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.16408066357755</v>
       </c>
       <c r="E35">
-        <v>-18.91609916395181</v>
+        <v>-17.88212175072845</v>
       </c>
       <c r="F35">
-        <v>-2.047400475313391</v>
+        <v>-1.205361696898082</v>
       </c>
       <c r="G35">
-        <v>-2.91349972123257</v>
+        <v>-1.316959340009187</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.57777170475878</v>
       </c>
       <c r="E36">
-        <v>-17.62160769801519</v>
+        <v>-17.4870078650852</v>
       </c>
       <c r="F36">
-        <v>-1.696309377147863</v>
+        <v>-1.524245870442766</v>
       </c>
       <c r="G36">
-        <v>-2.178595027515299</v>
+        <v>-1.369428176261096</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.96164413095597</v>
       </c>
       <c r="E37">
-        <v>-17.67061031525219</v>
+        <v>-17.40276466312051</v>
       </c>
       <c r="F37">
-        <v>-1.731778412600932</v>
+        <v>-1.349015515156767</v>
       </c>
       <c r="G37">
-        <v>-2.900141669981611</v>
+        <v>-0.747681239621653</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.31422449033365</v>
       </c>
       <c r="E38">
-        <v>-18.52515147439561</v>
+        <v>-17.0208376937876</v>
       </c>
       <c r="F38">
-        <v>-2.198864969813072</v>
+        <v>-1.800768163375686</v>
       </c>
       <c r="G38">
-        <v>-2.101320273537631</v>
+        <v>-0.8874193668342898</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.62921517771147</v>
       </c>
       <c r="E39">
-        <v>-16.99167884965221</v>
+        <v>-16.88034178769963</v>
       </c>
       <c r="F39">
-        <v>-1.741558946525785</v>
+        <v>-1.331018404963545</v>
       </c>
       <c r="G39">
-        <v>-1.877308899077307</v>
+        <v>-0.6694596696197533</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.90194060799727</v>
       </c>
       <c r="E40">
-        <v>-18.0785126114931</v>
+        <v>-16.08645500941494</v>
       </c>
       <c r="F40">
-        <v>-1.633008025328133</v>
+        <v>-1.755338009903953</v>
       </c>
       <c r="G40">
-        <v>-1.204844404776229</v>
+        <v>-1.331846863299289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.12747792628607</v>
       </c>
       <c r="E41">
-        <v>-17.60069973352177</v>
+        <v>-15.999114331229</v>
       </c>
       <c r="F41">
-        <v>-2.210627786932825</v>
+        <v>-1.548384496560344</v>
       </c>
       <c r="G41">
-        <v>-0.659104283172913</v>
+        <v>-0.5008039271215827</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.30431318584526</v>
       </c>
       <c r="E42">
-        <v>-17.15475372714243</v>
+        <v>-15.46556952364528</v>
       </c>
       <c r="F42">
-        <v>-1.79166771908853</v>
+        <v>-1.562411241791948</v>
       </c>
       <c r="G42">
-        <v>-0.6774116000050827</v>
+        <v>-0.5855042347438361</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.42739535912828</v>
       </c>
       <c r="E43">
-        <v>-17.27280198757438</v>
+        <v>-15.42009911613426</v>
       </c>
       <c r="F43">
-        <v>-1.452845570525865</v>
+        <v>-1.882835350338436</v>
       </c>
       <c r="G43">
-        <v>-1.072588110482345</v>
+        <v>-0.2764118399242424</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.48943010394905</v>
       </c>
       <c r="E44">
-        <v>-16.35853025626978</v>
+        <v>-14.63516513096273</v>
       </c>
       <c r="F44">
-        <v>-1.980090653631514</v>
+        <v>-1.390531632650273</v>
       </c>
       <c r="G44">
-        <v>-0.7317277206679051</v>
+        <v>0.07727029276379486</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.48779873118415</v>
       </c>
       <c r="E45">
-        <v>-16.68470718209426</v>
+        <v>-14.95828533683204</v>
       </c>
       <c r="F45">
-        <v>-1.973230943168932</v>
+        <v>-1.502040653843322</v>
       </c>
       <c r="G45">
-        <v>-2.139686185792244</v>
+        <v>-0.3399445193683958</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.42135410528203</v>
       </c>
       <c r="E46">
-        <v>-15.32075345335399</v>
+        <v>-14.00684841934649</v>
       </c>
       <c r="F46">
-        <v>-2.334814971225721</v>
+        <v>-1.87113383240649</v>
       </c>
       <c r="G46">
-        <v>-1.396518370408952</v>
+        <v>0.6047030975349411</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.29352861288753</v>
       </c>
       <c r="E47">
-        <v>-15.04005599198854</v>
+        <v>-14.16115164268385</v>
       </c>
       <c r="F47">
-        <v>-2.07796640410929</v>
+        <v>-1.793348476548811</v>
       </c>
       <c r="G47">
-        <v>-1.116257516690871</v>
+        <v>-0.4570517572745747</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.10561919121436</v>
       </c>
       <c r="E48">
-        <v>-14.10054254656519</v>
+        <v>-14.03843905402399</v>
       </c>
       <c r="F48">
-        <v>-2.252772635285055</v>
+        <v>-2.017033354694164</v>
       </c>
       <c r="G48">
-        <v>-1.490935129188967</v>
+        <v>-0.2787226007106537</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.86795332925711</v>
       </c>
       <c r="E49">
-        <v>-14.4614528680285</v>
+        <v>-13.84082097680327</v>
       </c>
       <c r="F49">
-        <v>-2.810440339625919</v>
+        <v>-2.218599994817368</v>
       </c>
       <c r="G49">
-        <v>-1.564919200900599</v>
+        <v>0.2203917975175668</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.59212278764351</v>
       </c>
       <c r="E50">
-        <v>-13.31344395081799</v>
+        <v>-13.67117075505391</v>
       </c>
       <c r="F50">
-        <v>-2.568525580047157</v>
+        <v>-2.35333478125011</v>
       </c>
       <c r="G50">
-        <v>-0.8186328516193131</v>
+        <v>0.1061117655019254</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.29801605531917</v>
       </c>
       <c r="E51">
-        <v>-12.95447634470397</v>
+        <v>-12.23456218933458</v>
       </c>
       <c r="F51">
-        <v>-2.440551099988661</v>
+        <v>-2.215283211736558</v>
       </c>
       <c r="G51">
-        <v>-1.789291424824704</v>
+        <v>-0.01807010822167605</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.00320492686469</v>
       </c>
       <c r="E52">
-        <v>-14.2452544619543</v>
+        <v>-11.91097555064248</v>
       </c>
       <c r="F52">
-        <v>-2.721597107308269</v>
+        <v>-2.343069652394619</v>
       </c>
       <c r="G52">
-        <v>-1.666622470412549</v>
+        <v>-0.1594668187494877</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.72700016296084</v>
       </c>
       <c r="E53">
-        <v>-13.47505613120373</v>
+        <v>-11.90688181013955</v>
       </c>
       <c r="F53">
-        <v>-2.650166986164868</v>
+        <v>-2.339288155200839</v>
       </c>
       <c r="G53">
-        <v>-1.51299660466267</v>
+        <v>0.02946270463117965</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.49050039782353</v>
       </c>
       <c r="E54">
-        <v>-12.00914833865477</v>
+        <v>-11.29921946847229</v>
       </c>
       <c r="F54">
-        <v>-2.846555501653172</v>
+        <v>-2.415759720357678</v>
       </c>
       <c r="G54">
-        <v>-1.493186300155671</v>
+        <v>0.1161692028502313</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.31397778980039</v>
       </c>
       <c r="E55">
-        <v>-13.82591324037002</v>
+        <v>-10.73893855034728</v>
       </c>
       <c r="F55">
-        <v>-2.727727854456389</v>
+        <v>-2.503554239543384</v>
       </c>
       <c r="G55">
-        <v>-1.378621561223652</v>
+        <v>-0.3179624969876351</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.21409156544791</v>
       </c>
       <c r="E56">
-        <v>-13.82361730404813</v>
+        <v>-10.75798531202354</v>
       </c>
       <c r="F56">
-        <v>-2.746292396320528</v>
+        <v>-2.621805343027819</v>
       </c>
       <c r="G56">
-        <v>-1.125676018750098</v>
+        <v>-0.403195802441711</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.19758865259037</v>
       </c>
       <c r="E57">
-        <v>-12.62739372407796</v>
+        <v>-10.57601311249931</v>
       </c>
       <c r="F57">
-        <v>-3.106494707549448</v>
+        <v>-2.609457698521689</v>
       </c>
       <c r="G57">
-        <v>-1.454565475894533</v>
+        <v>0.00187923919797212</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.27118057393335</v>
       </c>
       <c r="E58">
-        <v>-12.26892425010478</v>
+        <v>-10.4539707379926</v>
       </c>
       <c r="F58">
-        <v>-3.075442527088106</v>
+        <v>-2.956399504366595</v>
       </c>
       <c r="G58">
-        <v>-0.5072760436508579</v>
+        <v>-0.6694960856206853</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.43199692031121</v>
       </c>
       <c r="E59">
-        <v>-11.21391207511579</v>
+        <v>-10.7613861960033</v>
       </c>
       <c r="F59">
-        <v>-3.177030191897826</v>
+        <v>-2.802821844622372</v>
       </c>
       <c r="G59">
-        <v>-2.049963780586917</v>
+        <v>-0.3561297765098926</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.67805987474423</v>
       </c>
       <c r="E60">
-        <v>-13.28701577650923</v>
+        <v>-10.12640357064776</v>
       </c>
       <c r="F60">
-        <v>-2.939932388766343</v>
+        <v>-2.791774736938638</v>
       </c>
       <c r="G60">
-        <v>-1.036168799004823</v>
+        <v>-0.5132979259867922</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.99754326467695</v>
       </c>
       <c r="E61">
-        <v>-11.23346602588091</v>
+        <v>-9.682092343385186</v>
       </c>
       <c r="F61">
-        <v>-3.343853446412813</v>
+        <v>-2.766265162769427</v>
       </c>
       <c r="G61">
-        <v>-1.921077621652011</v>
+        <v>-0.8822317419742518</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.37871865208047</v>
       </c>
       <c r="E62">
-        <v>-12.97818743460813</v>
+        <v>-9.941030487143777</v>
       </c>
       <c r="F62">
-        <v>-3.461312630660172</v>
+        <v>-2.952970063319005</v>
       </c>
       <c r="G62">
-        <v>-2.202692488495654</v>
+        <v>-0.5054386908765623</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.80550426460681</v>
       </c>
       <c r="E63">
-        <v>-11.83530927844832</v>
+        <v>-8.359316028796661</v>
       </c>
       <c r="F63">
-        <v>-3.090122854200519</v>
+        <v>-2.952806046573251</v>
       </c>
       <c r="G63">
-        <v>-2.025657755237588</v>
+        <v>-1.001331928295072</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.26598842856732</v>
       </c>
       <c r="E64">
-        <v>-10.83031862734806</v>
+        <v>-8.874362020059047</v>
       </c>
       <c r="F64">
-        <v>-3.517702913238346</v>
+        <v>-3.043139511848537</v>
       </c>
       <c r="G64">
-        <v>-1.907405068574821</v>
+        <v>-1.207959628128683</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.74696140583851</v>
       </c>
       <c r="E65">
-        <v>-11.22192747410937</v>
+        <v>-9.637889908596316</v>
       </c>
       <c r="F65">
-        <v>-3.036288085059982</v>
+        <v>-2.961594196349551</v>
       </c>
       <c r="G65">
-        <v>-1.695354695147884</v>
+        <v>-2.034311521277243</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.23420781137126</v>
       </c>
       <c r="E66">
-        <v>-10.72037633538984</v>
+        <v>-8.885714904396277</v>
       </c>
       <c r="F66">
-        <v>-2.764576121635119</v>
+        <v>-2.993268480730396</v>
       </c>
       <c r="G66">
-        <v>-2.301664557937705</v>
+        <v>-1.116327038147196</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.71491350299134</v>
       </c>
       <c r="E67">
-        <v>-10.53510740678803</v>
+        <v>-8.855636780037331</v>
       </c>
       <c r="F67">
-        <v>-3.093204380938933</v>
+        <v>-2.900216313639121</v>
       </c>
       <c r="G67">
-        <v>-1.805155559048891</v>
+        <v>-0.7086631498958027</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.17497000851677</v>
       </c>
       <c r="E68">
-        <v>-10.18091281227809</v>
+        <v>-8.643704196478359</v>
       </c>
       <c r="F68">
-        <v>-2.979382557957267</v>
+        <v>-2.941593265408957</v>
       </c>
       <c r="G68">
-        <v>-1.789519852466913</v>
+        <v>-1.609095120576634</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.6027890864499</v>
       </c>
       <c r="E69">
-        <v>-11.43207583890932</v>
+        <v>-8.890904535609067</v>
       </c>
       <c r="F69">
-        <v>-3.173869970256146</v>
+        <v>-3.06557832805557</v>
       </c>
       <c r="G69">
-        <v>-2.785169733948262</v>
+        <v>-1.394270509987787</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.97972275153787</v>
       </c>
       <c r="E70">
-        <v>-10.58782337271132</v>
+        <v>-7.885574248958233</v>
       </c>
       <c r="F70">
-        <v>-2.934138787151164</v>
+        <v>-3.045339655670372</v>
       </c>
       <c r="G70">
-        <v>-1.861974452139403</v>
+        <v>-1.327572949008091</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.29412721829995</v>
       </c>
       <c r="E71">
-        <v>-10.50620215719707</v>
+        <v>-9.237052031807375</v>
       </c>
       <c r="F71">
-        <v>-3.154579778547154</v>
+        <v>-3.305006328691128</v>
       </c>
       <c r="G71">
-        <v>-2.544877096525802</v>
+        <v>-1.346754249862628</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.53590360639232</v>
       </c>
       <c r="E72">
-        <v>-10.1990991638929</v>
+        <v>-9.383901386928109</v>
       </c>
       <c r="F72">
-        <v>-3.463863173893392</v>
+        <v>-3.493475651808668</v>
       </c>
       <c r="G72">
-        <v>-1.865099607128474</v>
+        <v>-1.390612357166892</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.70853739303391</v>
       </c>
       <c r="E73">
-        <v>-10.07939801044814</v>
+        <v>-8.618530409469718</v>
       </c>
       <c r="F73">
-        <v>-3.215140890998423</v>
+        <v>-3.292303314569197</v>
       </c>
       <c r="G73">
-        <v>-1.775390444105304</v>
+        <v>-1.239608443484116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.81235695571921</v>
       </c>
       <c r="E74">
-        <v>-11.2509912202906</v>
+        <v>-8.612036577742719</v>
       </c>
       <c r="F74">
-        <v>-3.565828574238788</v>
+        <v>-3.178507999344421</v>
       </c>
       <c r="G74">
-        <v>-2.572755200512005</v>
+        <v>-0.4529301280781821</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.84986412352244</v>
       </c>
       <c r="E75">
-        <v>-10.1770183246315</v>
+        <v>-9.339046851882134</v>
       </c>
       <c r="F75">
-        <v>-3.413366725386136</v>
+        <v>-3.499514450175077</v>
       </c>
       <c r="G75">
-        <v>-1.191721402258558</v>
+        <v>-0.3079646494590361</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.82604796040242</v>
       </c>
       <c r="E76">
-        <v>-11.84925244991794</v>
+        <v>-9.630001306874954</v>
       </c>
       <c r="F76">
-        <v>-3.489385173573644</v>
+        <v>-3.404537157239697</v>
       </c>
       <c r="G76">
-        <v>-1.395843019118941</v>
+        <v>-0.6512218742439084</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.75166291338207</v>
       </c>
       <c r="E77">
-        <v>-11.59450767309045</v>
+        <v>-9.954208346506098</v>
       </c>
       <c r="F77">
-        <v>-3.492765740944469</v>
+        <v>-3.733022108982827</v>
       </c>
       <c r="G77">
-        <v>-1.751733285681672</v>
+        <v>-0.3271260870403377</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.639869135136</v>
       </c>
       <c r="E78">
-        <v>-11.29626237494528</v>
+        <v>-10.43999133873092</v>
       </c>
       <c r="F78">
-        <v>-3.652667985809066</v>
+        <v>-3.594265598809493</v>
       </c>
       <c r="G78">
-        <v>-1.985252546930783</v>
+        <v>-0.5309464442566469</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.49909094419639</v>
       </c>
       <c r="E79">
-        <v>-12.38009375851908</v>
+        <v>-10.64030385798621</v>
       </c>
       <c r="F79">
-        <v>-4.085369840498402</v>
+        <v>-3.698206655410566</v>
       </c>
       <c r="G79">
-        <v>-0.8127003540129391</v>
+        <v>0.4827558420503477</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.34245190143641</v>
       </c>
       <c r="E80">
-        <v>-13.29162576304904</v>
+        <v>-11.38929534495886</v>
       </c>
       <c r="F80">
-        <v>-4.054323458608879</v>
+        <v>-3.857225860623779</v>
       </c>
       <c r="G80">
-        <v>-1.654297309369843</v>
+        <v>-0.5468105784808345</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.17829302868442</v>
       </c>
       <c r="E81">
-        <v>-12.90697265236351</v>
+        <v>-12.08138202755112</v>
       </c>
       <c r="F81">
-        <v>-3.998359785243148</v>
+        <v>-3.854385388799579</v>
       </c>
       <c r="G81">
-        <v>-1.392112034296182</v>
+        <v>-0.5022572566133228</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.01878157106793</v>
       </c>
       <c r="E82">
-        <v>-13.34916002531649</v>
+        <v>-12.2114896142655</v>
       </c>
       <c r="F82">
-        <v>-3.941248823024538</v>
+        <v>-3.876665158465275</v>
       </c>
       <c r="G82">
-        <v>-2.067559330128143</v>
+        <v>-0.1013468812620428</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.86712583562292</v>
       </c>
       <c r="E83">
-        <v>-13.58529277397245</v>
+        <v>-14.38754364374931</v>
       </c>
       <c r="F83">
-        <v>-4.012752668866788</v>
+        <v>-4.185224560701466</v>
       </c>
       <c r="G83">
-        <v>-0.8895646003437375</v>
+        <v>0.5753451796926842</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.7292569174649</v>
       </c>
       <c r="E84">
-        <v>-14.51741574981529</v>
+        <v>-14.03243882596383</v>
       </c>
       <c r="F84">
-        <v>-4.43064662786368</v>
+        <v>-3.802928034105077</v>
       </c>
       <c r="G84">
-        <v>-1.296728596218701</v>
+        <v>0.2616213316636502</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.60511487075708</v>
       </c>
       <c r="E85">
-        <v>-17.75969898440509</v>
+        <v>-15.63535559961486</v>
       </c>
       <c r="F85">
-        <v>-4.338724353909825</v>
+        <v>-4.270508298289286</v>
       </c>
       <c r="G85">
-        <v>-1.462537269553098</v>
+        <v>0.3045524862169189</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.49387228368709</v>
       </c>
       <c r="E86">
-        <v>-16.74646198213686</v>
+        <v>-16.7099987094271</v>
       </c>
       <c r="F86">
-        <v>-4.119723893427303</v>
+        <v>-4.431028505236371</v>
       </c>
       <c r="G86">
-        <v>-1.695639402064261</v>
+        <v>-0.03944299022321084</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.38691192049605</v>
       </c>
       <c r="E87">
-        <v>-18.95982610896987</v>
+        <v>-17.34974981791271</v>
       </c>
       <c r="F87">
-        <v>-4.127754915397444</v>
+        <v>-4.35600326956482</v>
       </c>
       <c r="G87">
-        <v>-1.2114257693083</v>
+        <v>1.252931087943014</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.27170688908134</v>
       </c>
       <c r="E88">
-        <v>-19.20756533650749</v>
+        <v>-19.16663698842617</v>
       </c>
       <c r="F88">
-        <v>-4.499424316583318</v>
+        <v>-4.450550639818148</v>
       </c>
       <c r="G88">
-        <v>-1.211657507496049</v>
+        <v>0.6589000385583497</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.14031952963486</v>
       </c>
       <c r="E89">
-        <v>-22.53180942216212</v>
+        <v>-20.6792288195202</v>
       </c>
       <c r="F89">
-        <v>-4.678045179648976</v>
+        <v>-4.721887352809542</v>
       </c>
       <c r="G89">
-        <v>-1.290759682611395</v>
+        <v>0.6244306384034581</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.98680321935237</v>
       </c>
       <c r="E90">
-        <v>-23.28347270879929</v>
+        <v>-21.72081406907645</v>
       </c>
       <c r="F90">
-        <v>-4.669730027659674</v>
+        <v>-4.685395283614016</v>
       </c>
       <c r="G90">
-        <v>-1.122630316853968</v>
+        <v>0.4689839726069795</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.81108300859198</v>
       </c>
       <c r="E91">
-        <v>-24.63668942566738</v>
+        <v>-24.41162879596017</v>
       </c>
       <c r="F91">
-        <v>-4.451502433963964</v>
+        <v>-4.566532016618911</v>
       </c>
       <c r="G91">
-        <v>-2.076365381262605</v>
+        <v>0.1101208361499828</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.61218226692862</v>
       </c>
       <c r="E92">
-        <v>-25.67158159064028</v>
+        <v>-26.28739518552135</v>
       </c>
       <c r="F92">
-        <v>-4.555256279532005</v>
+        <v>-4.705481536397098</v>
       </c>
       <c r="G92">
-        <v>-1.768858737756322</v>
+        <v>-0.2331595624536643</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.40499707387626</v>
       </c>
       <c r="E93">
-        <v>-28.19222532126377</v>
+        <v>-28.01936441144297</v>
       </c>
       <c r="F93">
-        <v>-4.835660302114443</v>
+        <v>-4.745408016844631</v>
       </c>
       <c r="G93">
-        <v>-2.229474801908358</v>
+        <v>-0.1934727425288814</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.20591821131216</v>
       </c>
       <c r="E94">
-        <v>-29.85830525037378</v>
+        <v>-29.92705880699524</v>
       </c>
       <c r="F94">
-        <v>-5.014750021130085</v>
+        <v>-4.755390672415768</v>
       </c>
       <c r="G94">
-        <v>-2.604764865331218</v>
+        <v>-0.5118710808593663</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.04031112590107</v>
       </c>
       <c r="E95">
-        <v>-31.77803406560143</v>
+        <v>-32.40167286356775</v>
       </c>
       <c r="F95">
-        <v>-4.838711179258953</v>
+        <v>-4.979899776126907</v>
       </c>
       <c r="G95">
-        <v>-3.281019934274761</v>
+        <v>-0.0679997560449641</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.93395573022986</v>
       </c>
       <c r="E96">
-        <v>-35.13763194783394</v>
+        <v>-34.08029666567901</v>
       </c>
       <c r="F96">
-        <v>-4.951825576478629</v>
+        <v>-4.983726005160438</v>
       </c>
       <c r="G96">
-        <v>-2.85281742149773</v>
+        <v>-0.8840790263851651</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.90488888703444</v>
       </c>
       <c r="E97">
-        <v>-37.13212586892823</v>
+        <v>-35.7635983814402</v>
       </c>
       <c r="F97">
-        <v>-4.921504016066556</v>
+        <v>-5.037231912442063</v>
       </c>
       <c r="G97">
-        <v>-2.612643963714683</v>
+        <v>-1.006125598235937</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.98431203145921</v>
       </c>
       <c r="E98">
-        <v>-38.77464867625034</v>
+        <v>-38.813412413756</v>
       </c>
       <c r="F98">
-        <v>-4.666541641526298</v>
+        <v>-5.009917325702153</v>
       </c>
       <c r="G98">
-        <v>-3.272141051138436</v>
+        <v>-1.79484983078514</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.16693787645578</v>
       </c>
       <c r="E99">
-        <v>-42.00136301720177</v>
+        <v>-41.33517920593338</v>
       </c>
       <c r="F99">
-        <v>-5.294697613273581</v>
+        <v>-5.056071472283932</v>
       </c>
       <c r="G99">
-        <v>-3.402384533744443</v>
+        <v>-1.899529280736895</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.48075042462639</v>
       </c>
       <c r="E100">
-        <v>-44.76198190667672</v>
+        <v>-43.71712936312395</v>
       </c>
       <c r="F100">
-        <v>-5.090878642182165</v>
+        <v>-5.217986649937332</v>
       </c>
       <c r="G100">
-        <v>-3.413978064222971</v>
+        <v>-2.719071381711174</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.86705131174416</v>
       </c>
       <c r="E101">
-        <v>-46.42530399511607</v>
+        <v>-46.72083447309364</v>
       </c>
       <c r="F101">
-        <v>-4.834654664087444</v>
+        <v>-4.84241480991687</v>
       </c>
       <c r="G101">
-        <v>-4.48693580513738</v>
+        <v>-2.788728570402979</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.38593484719211</v>
       </c>
       <c r="E102">
-        <v>-49.1660734508969</v>
+        <v>-48.90222078072149</v>
       </c>
       <c r="F102">
-        <v>-5.134336452867832</v>
+        <v>-4.842921770767384</v>
       </c>
       <c r="G102">
-        <v>-4.274736457161175</v>
+        <v>-3.514734517710689</v>
       </c>
     </row>
   </sheetData>
